--- a/data/GreatLink/GreatLink Income Focus_Dividends.xlsx
+++ b/data/GreatLink/GreatLink Income Focus_Dividends.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="DividendHistory" sheetId="1" r:id="GemRid661712"/>
+    <sheet name="DividendHistory" sheetId="1" r:id="GemRid319779"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>XD Date</t>
   </si>
@@ -26,6 +26,12 @@
     <t>Gross Dividend</t>
   </si>
   <si>
+    <t>06/11/2025</t>
+  </si>
+  <si>
+    <t>0.017</t>
+  </si>
+  <si>
     <t>06/05/2025</t>
   </si>
   <si>
@@ -51,9 +57,6 @@
   </si>
   <si>
     <t>09/05/2022</t>
-  </si>
-  <si>
-    <t>0.017</t>
   </si>
   <si>
     <t>05/11/2021</t>
@@ -469,29 +472,29 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -502,29 +505,29 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -535,29 +538,29 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
         <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
         <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -579,7 +582,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -590,7 +593,7 @@
         <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -601,7 +604,7 @@
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -612,7 +615,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -623,7 +626,7 @@
         <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -634,7 +637,7 @@
         <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -642,43 +645,54 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" t="s">
         <v>27</v>
       </c>
-      <c r="B20" t="s">
-        <v>28</v>
-      </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" t="s">
         <v>29</v>
       </c>
-      <c r="B21" t="s">
-        <v>30</v>
-      </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" t="s">
         <v>31</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
         <v>32</v>
       </c>
-      <c r="C22" t="s">
-        <v>16</v>
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
